--- a/Filtered_V3.0/COCCL_HoustonClearLake.xlsx
+++ b/Filtered_V3.0/COCCL_HoustonClearLake.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alere (EPOC)-</t>
+          <t>Alere (EPOC)-ADMO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1627,7 +1627,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -1649,7 +1664,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (EPOC)-Admissions </t>
+          <t>Alere (EPOC)-labpoc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1694,22 +1709,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1838,7 +1838,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -1860,7 +1875,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1905,22 +1920,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bamboo Health (Bamboo)-Admissions </t>
+          <t>Bamboo Health (Bamboo)-ADMO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Champion Medical (UdiTracker)-Tissue Tracking </t>
+          <t>Champion Medical (UdiTracker)-SURTSD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeliverHealth (eScription One)-Admissions </t>
+          <t>DeliverHealth (eScription One)-ADMO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dicom Systems (Dicom Systems)-</t>
+          <t>Dicom Systems (Dicom Systems)-radord</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS DI Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3134,17 +3134,17 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSDIRO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3298,17 +3298,17 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Scheduling </t>
+          <t>GE (CMI - Carescape Gateway)-CWSO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN QS OB Link)-Admissions </t>
+          <t>GE (CPN QS OB Link)-ADMO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN QS OB Link)-Clinical Monitoring Results </t>
+          <t>GE (CPN QS OB Link)-ITSHMRO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PCSCMI</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical Monitoring Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN QS OB Link)-ITS HM Results </t>
+          <t>GE (CPN QS OB Link)-LABRES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN QS OB Link)-Lab Results (Discrete) </t>
+          <t>GE (CPN QS OB Link)-PCSCMI</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>PCSCMI</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">Clinical Monitoring Results </t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4136,6 +4136,21 @@
       <c r="P49" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4157,7 +4172,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4202,7 +4217,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4239,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-riurl</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4269,22 +4284,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4721,22 +4721,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4803,22 +4803,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5092,6 +5092,21 @@
       <c r="P62" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -5113,7 +5128,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5163,17 +5178,17 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5210,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5245,17 +5260,17 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5292,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5327,7 +5342,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5337,7 +5352,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -5359,7 +5374,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5409,7 +5424,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -5419,7 +5434,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5441,7 +5456,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5491,17 +5506,17 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -5523,7 +5538,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5605,7 +5620,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5687,7 +5702,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5737,17 +5752,17 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5784,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5819,17 +5834,17 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5866,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5901,17 +5916,17 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5948,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5979,21 +5994,6 @@
       <c r="P73" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greater Houston Health (Greater Houston Health)-Admissions </t>
+          <t>Greater Houston Health (Greater Houston Health)-ADMO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greater Houston Health (Greater Houston Health)-ITS DI Results </t>
+          <t>Greater Houston Health (Greater Houston Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greater Houston Health (Greater Houston Health)-ITS HM Results </t>
+          <t>Greater Houston Health (Greater Houston Health)-ITSHMRO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greater Houston Health (Greater Houston Health)-Lab Results (Discrete) </t>
+          <t>Greater Houston Health (Greater Houston Health)-LABRES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Greater Houston Health (Greater Houston Health)-Pathology Results</t>
+          <t>Greater Houston Health (Greater Houston Health)-LABRES2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6595,6 +6595,21 @@
       <c r="P81" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6616,7 +6631,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6662,6 +6677,21 @@
       <c r="P82" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>iPeople Scheduling</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6713,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6733,17 +6763,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -6765,7 +6795,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6815,17 +6845,17 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6877,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6929,7 +6959,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6979,7 +7009,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -6989,7 +7019,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -7011,7 +7041,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7061,7 +7091,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7071,7 +7101,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -7093,7 +7123,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7175,7 +7205,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7225,17 +7255,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -7257,7 +7287,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7307,17 +7337,17 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7369,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7421,7 +7451,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7471,17 +7501,17 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7533,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7585,7 +7615,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7635,17 +7665,17 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7697,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7717,17 +7747,17 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7779,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7799,17 +7829,17 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7861,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7881,17 +7911,17 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7943,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7963,17 +7993,17 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7995,7 +8025,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8041,21 +8071,6 @@
       <c r="P99" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8092,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8123,21 +8138,6 @@
       <c r="P100" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Orbit Azure)-Admissions </t>
+          <t>HCA (Orbit Azure)-ADMO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8539,7 +8539,22 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -8561,7 +8576,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8628,7 +8643,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8673,22 +8688,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform to UDS PROi)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform to UDS PROi)-ITSHMRO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8962,6 +8962,21 @@
       <c r="P112" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -8983,7 +8998,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9033,17 +9048,17 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9080,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9115,17 +9130,17 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -9147,7 +9162,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9197,17 +9212,17 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9279,7 +9294,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -9289,7 +9304,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -9311,7 +9326,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9361,7 +9376,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -9371,7 +9386,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -9393,7 +9408,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9443,17 +9458,17 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -9475,7 +9490,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9525,17 +9540,17 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9572,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9639,7 +9654,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9721,7 +9736,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9771,17 +9786,17 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -9803,7 +9818,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9853,17 +9868,17 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9900,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9935,17 +9950,17 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9982,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople EDM</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -10017,17 +10032,17 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10064,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Meds</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10099,17 +10114,17 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10146,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople PCS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10181,17 +10196,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10228,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10259,21 +10274,6 @@
       <c r="P128" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10357,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Null-Terminates Message)-</t>
+          <t>HCA D&amp;IS (Null-Terminates Message)-iti08</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10758,6 +10758,21 @@
       <c r="P135" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -10779,7 +10794,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10829,17 +10844,17 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -10861,7 +10876,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10911,17 +10926,17 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10943,7 +10958,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10993,17 +11008,17 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11040,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11107,7 +11122,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -11157,7 +11172,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -11167,7 +11182,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -11189,7 +11204,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -11239,17 +11254,17 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -11271,7 +11286,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -11321,17 +11336,17 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -11353,7 +11368,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11403,17 +11418,17 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11450,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11490,12 +11505,12 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11532,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11567,17 +11582,17 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -11599,7 +11614,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11681,7 +11696,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11731,17 +11746,17 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11778,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11813,17 +11828,17 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11860,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11895,17 +11910,17 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11942,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11977,17 +11992,17 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12024,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -12055,21 +12070,6 @@
       <c r="P151" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA-GCD Division (GCD-HermeTech UltraPort)-Admissions </t>
+          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-ADMO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA-GCD Division (GCD-HermeTech UltraPort)-Lab Results (Discrete) </t>
+          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-LABRES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA-GCD Division (GCD-HermeTech UltraPort)-OM Orders </t>
+          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-OMORDO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA-GCD Division (GCD-HermeTech UltraPort)-Pharmacy Orders </t>
+          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-PHAORD</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA-GCD Division (GCD-HermeTech UltraPort)-Tissue Tracking </t>
+          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-SURTSD</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-iPeople ED Patient Visit Data</t>
+          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-iPeople EDM</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-iPeople Medication Administration</t>
+          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-iPeople Meds</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-iPeople Nursing Assessment Forms</t>
+          <t>HCA-GCD Division (GCD-HermeTech UltraPort)-iPeople PCS</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haemonetics (TEG Manager)-Admissions </t>
+          <t>Haemonetics (TEG Manager)-ADMO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Healogics (iHeal/NetHealth WoundExpert)-Admissions </t>
+          <t>Healogics (iHeal/NetHealth WoundExpert)-ADMO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Healogics (iHeal/NetHealth WoundExpert)-Charges </t>
+          <t>Healogics (iHeal/NetHealth WoundExpert)-Patient Accounting</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS to Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS to Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -15089,7 +15089,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>IBM (Merge Cardio and Hemo to MPF-Patient Folder/HPF Facility)-</t>
+          <t>IBM (Merge Cardio and Hemo to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Merge Cardio and Hemo)-Admissions </t>
+          <t>IBM (Merge Cardio and Hemo)-ADMO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Merge Cardio and Hemo)-Charges </t>
+          <t>IBM (Merge Cardio and Hemo)-ITSHMRO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15767,17 +15767,17 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Merge Cardio and Hemo)-ITS HM Results </t>
+          <t>IBM (Merge Cardio and Hemo)-LABRES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -15844,12 +15844,12 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Merge Cardio and Hemo)-Lab Results (Discrete) </t>
+          <t>IBM (Merge Cardio and Hemo)-OMORDO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15931,17 +15931,17 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Merge Cardio and Hemo)-OM Orders </t>
+          <t>IBM (Merge Cardio and Hemo)-Patient Accounting</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -16008,22 +16008,22 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -16379,6 +16379,21 @@
       <c r="P208" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -16400,7 +16415,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16450,17 +16465,17 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -16482,7 +16497,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -16532,7 +16547,7 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -16542,7 +16557,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -16564,7 +16579,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16614,7 +16629,7 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -16624,7 +16639,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -16646,7 +16661,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16696,7 +16711,7 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -16706,7 +16721,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16743,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -16810,7 +16825,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16860,17 +16875,17 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -16892,7 +16907,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16942,17 +16957,17 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16989,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople ED Patient Visit Data</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -17024,17 +17039,17 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17071,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Medication Administration</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople PCS</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -17106,17 +17121,17 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -17138,7 +17153,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Nursing Assessment Forms</t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17184,21 +17199,6 @@
       <c r="P218" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">LabCorp (LabCorp)-Ref Lab Orders </t>
+          <t>LabCorp (LabCorp)-LABRR</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -17327,22 +17327,22 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>LABSO</t>
+          <t>LABRR</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ref Lab Orders </t>
+          <t>Ref Lab Results</t>
         </is>
       </c>
     </row>
@@ -17364,7 +17364,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>LabCorp (LabCorp)-Ref Lab Results</t>
+          <t>LabCorp (LabCorp)-LABSO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17409,22 +17409,22 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>LABRR</t>
+          <t>LABSO</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>Ref Lab Results</t>
+          <t xml:space="preserve">Ref Lab Orders </t>
         </is>
       </c>
     </row>
@@ -17508,7 +17508,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCR Technologies (Health Touch)-Admissions </t>
+          <t>MCR Technologies (Health Touch)-ADMO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCR Technologies (Health Touch)-OM Orders </t>
+          <t>MCR Technologies (Health Touch)-OMORDO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>MCR Technologies (Health Touch)-iPeople ED Patient Visit Data</t>
+          <t>MCR Technologies (Health Touch)-iPeople EDM</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>MCR Technologies (Health Touch)-iPeople Nursing Assessment Forms</t>
+          <t>MCR Technologies (Health Touch)-iPeople PCS</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17898,7 +17898,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>McKesson (Horizon Imaging)-</t>
+          <t>McKesson (Horizon Imaging)-ADMO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -17944,6 +17944,21 @@
       <c r="P228" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -17965,7 +17980,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (Horizon Imaging)-Admissions </t>
+          <t>McKesson (Horizon Imaging)-ITSDIRO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -18015,17 +18030,17 @@
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -18047,7 +18062,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (Horizon Imaging)-ITS DI Results </t>
+          <t>McKesson (Horizon Imaging)-ITSDIUI</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18092,22 +18107,22 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -18129,7 +18144,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (Horizon Imaging)-Radiology Image Status </t>
+          <t>McKesson (Horizon Imaging)-radord</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18174,22 +18189,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R231" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-</t>
+          <t>Meditech (HCA 5.6)-ADMO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18463,6 +18463,21 @@
       <c r="P235" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -18484,7 +18499,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Admissions </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18534,17 +18549,17 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -18566,7 +18581,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -18616,7 +18631,7 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -18626,7 +18641,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -18648,7 +18663,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS HM Results </t>
+          <t>Meditech (HCA 5.6)-LABRES</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18698,7 +18713,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -18708,7 +18723,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -18730,7 +18745,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Lab Results (Discrete) </t>
+          <t>Meditech (HCA 5.6)-OMORDO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18780,17 +18795,17 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -18812,7 +18827,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-OM Orders </t>
+          <t>Meditech (HCA 5.6)-PHAORD</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18862,17 +18877,17 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -18894,7 +18909,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Pharmacy Orders </t>
+          <t>Meditech (HCA 5.6)-radord</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18940,21 +18955,6 @@
       <c r="P241" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R241" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -19038,7 +19038,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-Admissions </t>
+          <t>Mednax (BabySteps Cloud)-ADMO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-ITS HM Results </t>
+          <t>Mednax (BabySteps Cloud)-ITSHMRO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility to Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility to Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -19880,7 +19880,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Lab Results (Discrete) </t>
+          <t>Midas+ (Care Management-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Admissions </t>
+          <t>Net Health (ReDoc Xfit)-ADMO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Charges </t>
+          <t>Net Health (ReDoc Xfit)-Patient Accounting</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Netsmart (UDS PROi to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Netsmart (UDS PROi to PA)-Case Mix Group</t>
+          <t>Netsmart (UDS PROi to PA)-nan</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi)-Admissions </t>
+          <t>Netsmart (UDS PROi)-ADMO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi)-Admissions </t>
+          <t>Netsmart (UDS PROi)-ADMO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Nuance (Dictaphone PowerScribe 360)-</t>
+          <t>Nuance (Dictaphone PowerScribe 360)-ITSDIRO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -21276,7 +21276,22 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -21298,7 +21313,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuance (Dictaphone PowerScribe 360)-ITS DI Results </t>
+          <t>Nuance (Dictaphone PowerScribe 360)-radord</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21343,22 +21358,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R273" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuance (EditScript)-ITS HM Results </t>
+          <t>Nuance (EditScript)-ITSHMRO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22131,6 +22131,21 @@
       <c r="P284" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -22152,7 +22167,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22198,21 +22213,6 @@
       <c r="P285" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q285" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R285" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precision Document Solutions (eDemand)-Admissions </t>
+          <t>Precision Document Solutions (eDemand)-ADMO</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE to MD - CMORE)-ITS HM Results </t>
+          <t>Provation (MD - CMORE to MD - CMORE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -22630,6 +22630,21 @@
       <c r="P291" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>SCAIMG</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>MDM</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scanned Documents </t>
         </is>
       </c>
     </row>
@@ -22651,7 +22666,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22697,21 +22712,6 @@
       <c r="P292" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>SCAIMG</t>
-        </is>
-      </c>
-      <c r="R292" t="inlineStr">
-        <is>
-          <t>MDM</t>
-        </is>
-      </c>
-      <c r="S292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scanned Documents </t>
         </is>
       </c>
     </row>
@@ -22795,7 +22795,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-Admissions </t>
+          <t>Provation (MD - CMORE)-ADMO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -22877,7 +22877,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-Scheduling </t>
+          <t>Provation (MD - CMORE)-CWSO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -23021,7 +23021,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q-Centrix (Q-Apps)-Admissions </t>
+          <t>Q-Centrix (Q-Apps)-ADMO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Radiology Partners (Rad Partners)-</t>
+          <t>Radiology Partners (Rad Partners)-ADMO</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -23211,6 +23211,21 @@
       <c r="P299" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -23232,7 +23247,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiology Partners (Rad Partners)-Admissions </t>
+          <t>Radiology Partners (Rad Partners)-ITSDIRO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -23277,22 +23292,22 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -23314,7 +23329,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiology Partners (Rad Partners)-ITS DI Results </t>
+          <t>Radiology Partners (Rad Partners)-ITSDIRO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -23359,7 +23374,7 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
@@ -23396,7 +23411,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiology Partners (Rad Partners)-ITS DI Results </t>
+          <t>Radiology Partners (Rad Partners)-radord</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -23442,21 +23457,6 @@
       <c r="P302" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q302" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R302" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rauland (Responder)-Admissions </t>
+          <t>Rauland (Responder)-ADMO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScottCare (TeleRehab VersaCare to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>ScottCare (TeleRehab VersaCare to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScottCare (TeleRehab VersaCare)-Admissions </t>
+          <t>ScottCare (TeleRehab VersaCare)-ADMO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sisco (FastPass)-Admissions </t>
+          <t>Sisco (FastPass)-ADMO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team Health (Team Health)-Admissions </t>
+          <t>Team Health (Team Health)-ADMO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Telcor (Quick-Link)-</t>
+          <t>Telcor (Quick-Link)-ADMO</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -24305,7 +24305,22 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -24327,7 +24342,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telcor (Quick-Link)-Admissions </t>
+          <t>Telcor (Quick-Link)-labpoc</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -24372,22 +24387,7 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R315" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -24553,7 +24553,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -24635,7 +24635,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -24779,7 +24779,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -24943,7 +24943,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -25025,7 +25025,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -25107,7 +25107,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople ED Patient Visit Data</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -25353,7 +25353,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Medication Administration</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Nursing Assessment Forms</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople PCS</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -25579,7 +25579,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Virtual Radiologic (Virtual Radiologic)-</t>
+          <t>Virtual Radiologic (Virtual Radiologic)-ADMO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -25625,6 +25625,21 @@
       <c r="P331" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -25646,7 +25661,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virtual Radiologic (Virtual Radiologic)-Admissions </t>
+          <t>Virtual Radiologic (Virtual Radiologic)-ITSDIRO</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -25696,17 +25711,17 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -25728,7 +25743,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virtual Radiologic (Virtual Radiologic)-ITS DI Results </t>
+          <t>Virtual Radiologic (Virtual Radiologic)-ITSDIRO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -25773,7 +25788,7 @@
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q333" t="inlineStr">
@@ -25810,7 +25825,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virtual Radiologic (Virtual Radiologic)-ITS DI Results </t>
+          <t>Virtual Radiologic (Virtual Radiologic)-radord</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -25855,22 +25870,7 @@
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q334" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R334" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -25954,7 +25954,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -26000,6 +26000,21 @@
       <c r="P336" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -26021,7 +26036,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -26071,17 +26086,17 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -26103,7 +26118,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -26185,7 +26200,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -26267,7 +26282,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -26349,7 +26364,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -26399,17 +26414,17 @@
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26446,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -26481,17 +26496,17 @@
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -26513,7 +26528,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -26563,17 +26578,17 @@
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -26595,7 +26610,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -26645,17 +26660,17 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26692,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -26723,21 +26738,6 @@
       <c r="P345" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q345" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R345" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S345" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -26821,7 +26821,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (HCA 5.6)-iPeople EDM</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -26985,7 +26985,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (HCA 5.6)-iPeople PCS</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -27129,7 +27129,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople)-OM Orders </t>
+          <t>iPeople (iPeople)-OMORDO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -27211,7 +27211,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>iPeople (iPeople)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople)-iPeople PCS</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
